--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_認知症施策_法定記載事項と見込量への影響_20260916.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_認知症施策_法定記載事項と見込量への影響_20260916.xlsx
@@ -2020,10 +2020,10 @@
         <v>782</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="F13" s="4" t="n"/>
     </row>
@@ -2040,10 +2040,10 @@
         <v>335</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F14" s="4" t="n"/>
     </row>

--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_認知症施策_法定記載事項と見込量への影響_20260916.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_認知症施策_法定記載事項と見込量への影響_20260916.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>町内定員（令和7年度）</t>
+          <t>町内定員（令和6年度）</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
